--- a/03_26.xlsx
+++ b/03_26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sararagnarsdottir/Library/CloudStorage/OneDrive-ReykjavikUniversity/HR vor 2026/verkfr x/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{185885A6-84E6-3A46-979D-751A13B7B88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8EFC356-A670-984C-8A42-2FF99CB30B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" activeTab="1" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
+    <workbookView xWindow="900" yWindow="760" windowWidth="27980" windowHeight="16860" activeTab="2" xr2:uid="{7CFC1604-4118-4D2C-86E1-DDF4E62B5004}"/>
   </bookViews>
   <sheets>
     <sheet name="Events" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="151">
   <si>
     <t>Event</t>
   </si>
@@ -3445,8 +3445,8 @@
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>144</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -3543,13 +3543,13 @@
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>88</v>
+      <c r="A3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>89</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -3562,8 +3562,8 @@
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>90</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -3576,13 +3576,13 @@
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>91</v>
+      <c r="A6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>145</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3679,8 +3679,8 @@
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>146</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -3777,13 +3777,13 @@
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>92</v>
+      <c r="A9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>93</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -3814,23 +3814,23 @@
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>94</v>
+      <c r="A11">
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>95</v>
+      <c r="A12">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>96</v>
+      <c r="A13">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>97</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -3840,34 +3840,34 @@
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>98</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="U15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>99</v>
+      <c r="A16">
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>100</v>
+      <c r="A17">
+        <v>16</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>101</v>
+      <c r="A18">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>102</v>
+      <c r="A19">
+        <v>18</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -3916,18 +3916,18 @@
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>103</v>
+      <c r="A20">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>104</v>
+      <c r="A21">
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>147</v>
+      <c r="A22">
+        <v>21</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -4024,8 +4024,8 @@
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>105</v>
+      <c r="A23">
+        <v>22</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -4035,8 +4035,8 @@
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>148</v>
+      <c r="A24">
+        <v>23</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -4133,8 +4133,8 @@
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>106</v>
+      <c r="A25">
+        <v>24</v>
       </c>
       <c r="I25">
         <v>1</v>
@@ -4153,8 +4153,8 @@
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>149</v>
+      <c r="A26">
+        <v>25</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -4251,21 +4251,21 @@
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>107</v>
+      <c r="A27">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>108</v>
+      <c r="A28">
+        <v>27</v>
       </c>
       <c r="AF28">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>109</v>
+      <c r="A29">
+        <v>28</v>
       </c>
       <c r="U29">
         <v>1</v>
@@ -4275,8 +4275,8 @@
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>110</v>
+      <c r="A30">
+        <v>29</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -4289,18 +4289,18 @@
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>111</v>
+      <c r="A31">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>112</v>
+      <c r="A32">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>113</v>
+      <c r="A33">
+        <v>32</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -4334,8 +4334,8 @@
       </c>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>114</v>
+      <c r="A34">
+        <v>33</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -4348,8 +4348,8 @@
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>150</v>
+      <c r="A35">
+        <v>34</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -4392,18 +4392,18 @@
       </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>115</v>
+      <c r="A36">
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>116</v>
+      <c r="A37">
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>117</v>
+      <c r="A38">
+        <v>37</v>
       </c>
       <c r="P38">
         <v>1</v>
@@ -4413,24 +4413,24 @@
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>118</v>
+      <c r="A39">
+        <v>38</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>119</v>
+      <c r="A40">
+        <v>39</v>
       </c>
       <c r="W40">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>120</v>
+      <c r="A41">
+        <v>40</v>
       </c>
       <c r="V41">
         <v>1</v>
@@ -4452,8 +4452,8 @@
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>121</v>
+      <c r="A42">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4463,14 +4463,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC469287-6D87-488B-B523-72276289E9B7}">
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AQ43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="str">
         <f>Events!B1</f>
         <v>Event</v>
@@ -4615,8 +4615,36 @@
         <f>Employees!B35</f>
         <v>Vero</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AK1" s="1" t="str">
+        <f>Employees!B36</f>
+        <v xml:space="preserve">Védís </v>
+      </c>
+      <c r="AL1" s="1" t="str">
+        <f>Employees!B37</f>
+        <v xml:space="preserve">Unnar </v>
+      </c>
+      <c r="AM1" s="1" t="str">
+        <f>Employees!B38</f>
+        <v>Ömmi</v>
+      </c>
+      <c r="AN1" s="1" t="str">
+        <f>Employees!B39</f>
+        <v xml:space="preserve">Arnar </v>
+      </c>
+      <c r="AO1" s="1" t="str">
+        <f>Employees!B40</f>
+        <v xml:space="preserve">Róbert </v>
+      </c>
+      <c r="AP1" s="1" t="str">
+        <f>Employees!B41</f>
+        <v xml:space="preserve">Jara </v>
+      </c>
+      <c r="AQ1" s="1" t="str">
+        <f>Employees!B42</f>
+        <v xml:space="preserve">Þórey </v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <f>Events!B2</f>
         <v>JS</v>
@@ -4626,7 +4654,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <f>Events!B3</f>
         <v>Sinfó</v>
@@ -4636,7 +4664,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <f>Events!B4</f>
         <v>Tón</v>
@@ -4646,7 +4674,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <f>Events!B5</f>
         <v>RMF</v>
@@ -4656,7 +4684,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <f>Events!B6</f>
         <v>HAM</v>
@@ -4666,7 +4694,7 @@
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <f>Events!B7</f>
         <v>IS</v>
@@ -4676,7 +4704,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <f>Events!B8</f>
         <v>IS</v>
@@ -4686,7 +4714,7 @@
         <v>46088</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <f>Events!B9</f>
         <v>PD</v>
@@ -4696,7 +4724,7 @@
         <v>46090</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <f>Events!B10</f>
         <v>Sinfó</v>
@@ -4706,7 +4734,7 @@
         <v>46093</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <f>Events!B11</f>
         <v>Sinfó</v>
@@ -4716,7 +4744,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <f>Events!B12</f>
         <v>SB</v>
@@ -4726,7 +4754,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <f>Events!B13</f>
         <v>GB</v>
@@ -4736,7 +4764,7 @@
         <v>46095</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <f>Events!B14</f>
         <v>ITV</v>
@@ -4746,7 +4774,7 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <f>Events!B15</f>
         <v>DS</v>
@@ -4756,7 +4784,7 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <f>Events!B16</f>
         <v>DS</v>
